--- a/校园招聘/制造业/制造业通用/技术研发类/机械工程师/2_保留题目/5轮_制造业通用_机械工程师_可保留的题目.xlsx
+++ b/校园招聘/制造业/制造业通用/技术研发类/机械工程师/2_保留题目/5轮_制造业通用_机械工程师_可保留的题目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,52 +474,42 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>GPT5.5_是否删除</t>
+          <t>一审_是否删除</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>GPT5.5_错误类型</t>
+          <t>一审_删除原因</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>GPT5.5_删除原因</t>
+          <t>二审_是否删除</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Gemini3.1pro_是否删除</t>
+          <t>二审_删除原因</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Gemini3.1pro_错误类型</t>
+          <t>题目是否修改</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Gemini3.1pro_删除原因</t>
+          <t>是否重新出题</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>合并_是否删除</t>
+          <t>一审_错误大类集合</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>合并_错误类型</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>合并_删除原因</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>合并_建议动作</t>
+          <t>二审_错误大类集合</t>
         </is>
       </c>
     </row>
@@ -566,7 +556,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -585,26 +575,24 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>keep</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -649,7 +637,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -668,26 +656,24 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>keep</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -732,7 +718,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -751,26 +737,24 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>keep</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -815,7 +799,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -834,26 +818,24 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>keep</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -898,7 +880,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -917,26 +899,24 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>keep</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -981,7 +961,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1000,26 +980,24 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>keep</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1064,7 +1042,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1083,26 +1061,24 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>keep</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1147,7 +1123,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1166,26 +1142,24 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>keep</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1230,7 +1204,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1249,26 +1223,24 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>keep</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1313,7 +1285,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1332,26 +1304,24 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>keep</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1396,7 +1366,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1415,26 +1385,24 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>keep</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1479,7 +1447,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1498,26 +1466,24 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>keep</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1562,7 +1528,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1581,26 +1547,24 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>keep</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1645,7 +1609,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1664,26 +1628,24 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>keep</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
